--- a/task-reviews/diagrams/task_diagrams_cycle_offset_stage_label/task_diagrams_cycle_offset_stage_label.xlsx
+++ b/task-reviews/diagrams/task_diagrams_cycle_offset_stage_label/task_diagrams_cycle_offset_stage_label.xlsx
@@ -3029,7 +3029,263 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 1 step after Jud? Return the exact label shown. Answer using the exact visible label.
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 7 steps after Bill? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 7 steps after Bill? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[284.442, 665.777, 406.442, 723.777]], "answer": "Don"}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[284.442, 665.777, 406.442, 723.777]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>151044423209161</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0023.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="216.75" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 5 steps after Sill? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 5 steps after Sill? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[695.198, 714.242, 817.198, 772.242]], "answer": "Senn"}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[695.198, 714.242, 817.198, 772.242]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>243795328801702</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0011.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="216.75" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 5 steps after Bert? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer format: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 5 steps after Bert? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[539.0, 739.0, 661.0, 797.0]], "answer": "Puri"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[539.0, 739.0, 661.0, 797.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>414162578178819</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0022.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="216.75" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps after Hoyt? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps after Hoyt? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[415.873, 723.923, 537.873, 781.923]], "answer": "Katt"}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[415.873, 723.923, 537.873, 781.923]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>458542228865996</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0007.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="216.75" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps after Espy? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer requirement: set "answer" to the exact visible stage label.
@@ -3037,63 +3293,383 @@
 {"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 1 step after Jud? Return the exact label shown. Answer using the exact visible label.
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps after Espy? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[257.541, 333.128, 379.541, 391.128]], "answer": "Pen"}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[257.541, 333.128, 379.541, 391.128]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>780054758771778</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0005.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="216.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 7 steps after Adin? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer: set "answer" to the exact visible stage label.
 Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 7 steps after Adin? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
 {"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[850.769, 614.0, 972.769, 672.0]], "answer": "Dyun"}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[307.596, 297.489, 429.596, 355.489]], "answer": "Av"}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[307.596, 297.489, 429.596, 355.489]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>970509373405115</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0001.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="216.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 4 steps after Card? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer format: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 4 steps after Card? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[750.603, 286.746, 872.603, 344.746]], "answer": "Bred"}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[750.603, 286.746, 872.603, 344.746]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1518935437009259</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0021.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="216.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step after Fife? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step after Fife? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[179.0, 489.0, 301.0, 547.0]], "answer": "Acus"}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[179.0, 489.0, 301.0, 547.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1562806935281341</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0010.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="216.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps after Mac? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps after Mac? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[850.769, 614.0, 972.769, 672.0]], "answer": "Py"}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>[[850.769, 614.0, 972.769, 672.0]]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>500942214694776</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0015.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0015.json</t>
+      <c r="K10" t="n">
+        <v>1939983765062470</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0008.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0008.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="216.75" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="11" ht="216.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>after_k_steps</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 5 steps after Leal? Return the exact label shown. Return the exact visible label.
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps after Waki? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps after Waki? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[227.231, 614.0, 349.231, 672.0]], "answer": "Eran"}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[227.231, 614.0, 349.231, 672.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2242656048310531</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0002.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="216.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps after Shep? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer requirement: set "answer" to the exact visible stage label.
@@ -3101,63 +3677,127 @@
 {"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 5 steps after Leal? Return the exact label shown. Return the exact visible label.
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps after Shep? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[227.231, 364.0, 349.231, 422.0]], "answer": "Aggi"}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[227.231, 364.0, 349.231, 422.0]], "answer": "Hume"}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>[[227.231, 364.0, 349.231, 422.0]]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>809866733078856</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0000.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0000.json</t>
+      <c r="K12" t="n">
+        <v>2248939749749493</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0006.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0006.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="216.75" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="13" ht="216.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>after_k_steps</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 5 steps after Brig? Return the exact label shown. Answer using the exact visible label.
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step after Elsa? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step after Elsa? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[327.397, 691.254, 449.397, 749.254]], "answer": "Joli"}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[327.397, 691.254, 449.397, 749.254]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>2364747141474969</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0014.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="216.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps after Jeb? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer: set "answer" to the exact visible stage label.
@@ -3165,63 +3805,63 @@
 {"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 5 steps after Brig? Return the exact label shown. Answer using the exact visible label.
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps after Jeb? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[227.231, 364.0, 349.231, 422.0]], "answer": "Sida"}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[227.231, 364.0, 349.231, 422.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Jae"}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>2322219551241602</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0021.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0021.json</t>
+      <c r="K14" t="n">
+        <v>2372574080848618</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0013.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0013.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="216.75" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="15" ht="216.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>after_k_steps</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 3 steps after Rita? Return the exact label shown. Answer with the exact label shown.
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 5 steps after Arel? Return the exact label shown. Give the full label exactly as shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer requirement: set "answer" to the exact visible stage label.
@@ -3229,63 +3869,191 @@
 {"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 3 steps after Rita? Return the exact label shown. Answer with the exact label shown.
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 5 steps after Arel? Return the exact label shown. Give the full label exactly as shown.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
+Answer requirement: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[889.974, 544.63, 1011.974, 602.63]], "answer": "Wyne"}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[889.974, 544.63, 1011.974, 602.63]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[793.558, 665.777, 915.558, 723.777]], "answer": "Dal"}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[793.558, 665.777, 915.558, 723.777]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>2635826189726085</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0009.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0009.json</t>
+      <c r="K15" t="n">
+        <v>3230663386888084</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0017.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0017.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="216.75" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="16" ht="216.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>after_k_steps</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps after Judd? Return the exact label shown. Give the full label exactly as shown.
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps after Rab? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps after Rab? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[539.0, 739.0, 661.0, 797.0]], "answer": "Lin"}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[539.0, 739.0, 661.0, 797.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>3764172516678724</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0004.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="216.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 2 steps after Doy? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 2 steps after Doy? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[257.541, 333.128, 379.541, 391.128]], "answer": "Cher"}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[257.541, 333.128, 379.541, 391.128]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>3912121357397448</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0000.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="216.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step after Hola? Return the exact label shown. Give the full label exactly as shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer format: set "answer" to the exact visible stage label.
@@ -3293,63 +4061,127 @@
 {"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps after Judd? Return the exact label shown. Give the full label exactly as shown.
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step after Hola? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[227.231, 614.0, 349.231, 672.0]], "answer": "Wira"}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[227.231, 614.0, 349.231, 672.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>4087180633151600</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0019.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="216.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps after Ciri? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps after Ciri? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[196.62, 411.746, 318.62, 469.746]], "answer": "Per"}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[196.62, 411.746, 318.62, 469.746]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[850.769, 614.0, 972.769, 672.0]], "answer": "Zurn"}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[850.769, 614.0, 972.769, 672.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>2903205546887100</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0002.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0002.json</t>
+      <c r="K19" t="n">
+        <v>4112736260634765</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0016.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0016.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="216.75" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="20" ht="216.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>after_k_steps</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 6 steps after Mena? Return the exact label shown. Return the exact visible label.
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 1 step after Bale? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer field: set "answer" to the exact visible stage label.
@@ -3357,191 +4189,63 @@
 {"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 6 steps after Mena? Return the exact label shown. Return the exact visible label.
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 1 step after Bale? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
+Answer: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[307.596, 297.489, 429.596, 355.489]], "answer": "Olen"}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[307.596, 297.489, 429.596, 355.489]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[899.0, 489.0, 1021.0, 547.0]], "answer": "Pine"}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[899.0, 489.0, 1021.0, 547.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>2920130705208031</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0016.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0016.json</t>
+      <c r="K20" t="n">
+        <v>4249260253100614</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0003.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0003.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="216.75" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="21" ht="216.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>after_k_steps</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps after Pish? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps after Pish? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[899.0, 489.0, 1021.0, 547.0]], "answer": "Issi"}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[899.0, 489.0, 1021.0, 547.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3177130085366982</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0014.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="216.75" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps after Dev? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps after Dev? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[881.38, 566.254, 1003.38, 624.254]], "answer": "Voe"}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[881.38, 566.254, 1003.38, 624.254]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>3301040395376902</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0024.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="216.75" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps after Vita? Return the exact label shown. Return the exact visible label.
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 6 steps after Cate? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer rule: set "answer" to the exact visible stage label.
@@ -3549,63 +4253,255 @@
 {"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps after Vita? Return the exact label shown. Return the exact visible label.
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 6 steps after Cate? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible stage label.
+Answer rule: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[284.442, 312.223, 406.442, 370.223]], "answer": "Chet"}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[284.442, 312.223, 406.442, 370.223]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[327.397, 286.746, 449.397, 344.746]], "answer": "Ira"}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[327.397, 286.746, 449.397, 344.746]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>3853034783443525</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0004.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0004.json</t>
+      <c r="K21" t="n">
+        <v>4539101959585738</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0020.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="216.75" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
+    <row r="22" ht="216.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>after_k_steps</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 1 step after Hew? Return the exact label shown. Answer using the exact visible label.
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 1 step after Arun? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 1 step after Arun? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[770.404, 297.489, 892.404, 355.489]], "answer": "Kemp"}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[770.404, 297.489, 892.404, 355.489]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>6544971922093570</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0018.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="216.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps after Gitt? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer format: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps after Gitt? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[227.231, 614.0, 349.231, 672.0]], "answer": "Riba"}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[227.231, 614.0, 349.231, 672.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>6990156048224878</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0024.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="216.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps after Fi? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps after Fi? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Mina"}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[196.62, 411.746, 318.62, 469.746]], "answer": "Rolo"}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[196.62, 411.746, 318.62, 469.746]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>7086718816381157</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0012.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="216.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>after_k_steps</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 1 step after Kobi? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer: set "answer" to the exact visible stage label.
@@ -3613,575 +4509,63 @@
 {"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 1 step after Hew? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Jaal"}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>4524301524665620</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0011.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="216.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps after Cobb? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps after Cobb? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Dyun"}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>4634375423602077</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0012.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="216.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 6 steps after Rese? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 6 steps after Rese? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[257.541, 333.128, 379.541, 391.128]], "answer": "Nick"}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[257.541, 333.128, 379.541, 391.128]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>4811269939176798</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0018.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="216.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 5 steps after Raul? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 5 steps after Raul? Return the exact label shown. Respond with the exact label from the diagram.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 1 step after Kobi? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[893.531, 445.588, 1015.531, 503.588]], "answer": "Mady"}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[893.531, 445.588, 1015.531, 503.588]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[850.769, 364.0, 972.769, 422.0]], "answer": "Bael"}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[850.769, 364.0, 972.769, 422.0]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>4819184543406721</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0020.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0020.json</t>
+      <c r="K25" t="n">
+        <v>7363959444275967</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0015.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0015.json</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="216.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
+    <row r="26" ht="216.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>after_k_steps</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 4 steps after Tay? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 4 steps after Tay? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Fem"}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>5249416507398544</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0005.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="216.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps after Earl? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps after Earl? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[188.026, 544.63, 310.026, 602.63]], "answer": "Hoo"}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[188.026, 544.63, 310.026, 602.63]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>6130778507912929</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0008.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="216.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps after Gib? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps after Gib? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[695.198, 714.242, 817.198, 772.242]], "answer": "Suzi"}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[695.198, 714.242, 817.198, 772.242]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>6557202451803053</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0023.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="216.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps after Chas? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps after Chas? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[881.38, 566.254, 1003.38, 624.254]], "answer": "Tini"}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[881.38, 566.254, 1003.38, 624.254]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6679486926500588</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0006.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="216.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 2 steps after Ruby? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 2 steps after Ruby? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 739.0, 661.0, 797.0]], "answer": "Iyre"}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 739.0, 661.0, 797.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>6783426813566634</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0003.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="216.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps after Kone? Return the exact label shown. Return the exact visible label.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 2 steps after Adai? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer rule: set "answer" to the exact visible stage label.
@@ -4189,430 +4573,46 @@
 {"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps after Kone? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[196.62, 566.254, 318.62, 624.254]], "answer": "Odin"}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[196.62, 566.254, 318.62, 624.254]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>6973687850757300</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0010.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="216.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 8 steps after Behn? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 8 steps after Behn? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[327.397, 691.254, 449.397, 749.254]], "answer": "Clie"}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[327.397, 691.254, 449.397, 749.254]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>6982309258302774</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0017.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="216.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step after Trin? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step after Trin? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[662.127, 723.923, 784.127, 781.923]], "answer": "Erny"}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[662.127, 723.923, 784.127, 781.923]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7463569968917872</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0007.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="216.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 6 steps after Neil? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 6 steps after Neil? Return the exact label shown. Return the exact visible label.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 2 steps after Adai? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Mina"}</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[899.0, 489.0, 1021.0, 547.0]], "answer": "Ahl"}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[899.0, 489.0, 1021.0, 547.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[850.769, 364.0, 972.769, 422.0]], "answer": "Bear"}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[850.769, 364.0, 972.769, 422.0]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>7512642603965087</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0001.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="216.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps after Cown? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps after Cown? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[750.603, 691.254, 872.603, 749.254]], "answer": "Opal"}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[750.603, 691.254, 872.603, 749.254]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>7592184502585543</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0019.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="216.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 8 steps after Herm? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 8 steps after Herm? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[770.404, 297.489, 892.404, 355.489]], "answer": "Dan"}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[770.404, 297.489, 892.404, 355.489]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8060616166563750</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0022.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="216.75" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>after_k_steps</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 5 steps after Chud? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[747,242,869,300]],"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 5 steps after Chud? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Mina"}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[196.62, 411.746, 318.62, 469.746]], "answer": "Elsy"}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[196.62, 411.746, 318.62, 469.746]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8263592745951562</v>
+        <v>8623681364864763</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0013.png</t>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/after_k_steps/0009.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0013.json</t>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/after_k_steps/0009.json</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 1 step before Oz? Return the exact label shown. Give the full label exactly as shown.
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 1 step before Hebe? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer requirement: set "answer" to the exact visible stage label.
@@ -4736,21 +4736,21 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 1 step before Oz? Return the exact label shown. Give the full label exactly as shown.
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 1 step before Hebe? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
+Answer requirement: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Davi"}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[327.397, 691.254, 449.397, 749.254]], "answer": "Ochs"}</t>
+          <t>{"evidence": [[881.38, 411.746, 1003.38, 469.746]], "answer": "Vine"}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>[[327.397, 691.254, 449.397, 749.254]]</t>
+          <t>[[881.38, 411.746, 1003.38, 469.746]]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4764,16 +4764,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>91365224368843</v>
+        <v>590480819283076</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0017.png</t>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0020.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0017.json</t>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0020.json</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,519 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Gwyn? Return the exact label shown. Answer using the exact visible label.
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps before Lal? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps before Lal? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[820.459, 333.128, 942.459, 391.128]], "answer": "Ky"}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[820.459, 333.128, 942.459, 391.128]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1309544359677755</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0003.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="216.75" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 1 step before Meg? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 1 step before Meg? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[750.603, 691.254, 872.603, 749.254]], "answer": "Dosi"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[750.603, 691.254, 872.603, 749.254]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2223648629371893</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0012.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="216.75" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 5 steps before Jean? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 5 steps before Jean? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[284.442, 665.777, 406.442, 723.777]], "answer": "Gora"}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[284.442, 665.777, 406.442, 723.777]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2229733220490759</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0004.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="216.75" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 2 steps before Toft? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer format: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 2 steps before Toft? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[179.0, 489.0, 301.0, 547.0]], "answer": "Bik"}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[179.0, 489.0, 301.0, 547.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>3120970666244396</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0015.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="216.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps before Luis? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps before Luis? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[227.231, 364.0, 349.231, 422.0]], "answer": "Nick"}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[227.231, 364.0, 349.231, 422.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3160014764517441</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0017.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="216.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps before Olag? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps before Olag? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Glad"}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3300976405501700</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0021.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="216.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps before Er? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer format: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps before Er? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[539.0, 739.0, 661.0, 797.0]], "answer": "Hull"}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[539.0, 739.0, 661.0, 797.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>3426210012476887</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0008.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="216.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps before Kiri? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps before Kiri? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[188.026, 544.63, 310.026, 602.63]], "answer": "Shel"}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[188.026, 544.63, 310.026, 602.63]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3465334778480032</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0009.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="216.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 5 steps before Peti? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer field: set "answer" to the exact visible stage label.
@@ -4798,63 +5310,191 @@
 {"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Gwyn? Return the exact label shown. Answer using the exact visible label.
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 5 steps before Peti? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[227.231, 614.0, 349.231, 672.0]], "answer": "Jaye"}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[227.231, 614.0, 349.231, 672.0]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Kary"}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>407808798050278</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0018.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0018.json</t>
+      <c r="K11" t="n">
+        <v>3742486515867774</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0006.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0006.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="216.75" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="12" ht="216.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>before_k_steps</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 2 steps before Pike? Return the exact label shown. Answer with the exact label shown.
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 6 steps before Dyna? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 6 steps before Dyna? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[850.769, 614.0, 972.769, 672.0]], "answer": "Jeaz"}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[850.769, 614.0, 972.769, 672.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>4067016233806125</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0019.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="216.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 1 step before Des? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 1 step before Des? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[695.198, 714.242, 817.198, 772.242]], "answer": "Erny"}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[695.198, 714.242, 817.198, 772.242]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4942010914346230</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0000.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="216.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps before Dyl? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer format: set "answer" to the exact visible stage label.
@@ -4862,63 +5502,63 @@
 {"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 2 steps before Pike? Return the exact label shown. Answer with the exact label shown.
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps before Dyl? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
+Answer requirement: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[327.397, 691.254, 449.397, 749.254]], "answer": "Box"}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[327.397, 691.254, 449.397, 749.254]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[850.769, 364.0, 972.769, 422.0]], "answer": "Vola"}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[850.769, 364.0, 972.769, 422.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>408225388313391</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0023.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0023.json</t>
+      <c r="K14" t="n">
+        <v>5251913700568690</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0010.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0010.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="216.75" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="15" ht="216.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>before_k_steps</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps before Dirk? Return the exact label shown. Answer using the exact visible label.
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Brok? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer requirement: set "answer" to the exact visible stage label.
@@ -4926,63 +5566,127 @@
 {"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps before Dirk? Return the exact label shown. Answer using the exact visible label.
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Brok? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[284.442, 665.777, 406.442, 723.777]], "answer": "Oza"}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[284.442, 665.777, 406.442, 723.777]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>6365325919072305</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0024.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="216.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 5 steps before Luz? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer field: set "answer" to the exact visible stage label.
 Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 5 steps before Luz? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible stage label.
+Example JSON:
 {"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[227.231, 364.0, 349.231, 422.0]], "answer": "Hime"}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[227.231, 364.0, 349.231, 422.0]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[750.603, 286.746, 872.603, 344.746]], "answer": "Algy"}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[750.603, 286.746, 872.603, 344.746]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>506120219035646</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0013.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0013.json</t>
+      <c r="K16" t="n">
+        <v>6401540163171008</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0018.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0018.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="216.75" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="17" ht="216.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>before_k_steps</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 1 step before Roda? Return the exact label shown. Give the full label exactly as shown.
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 1 step before Iggy? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer format: set "answer" to the exact visible stage label.
@@ -4990,63 +5694,447 @@
 {"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 1 step before Roda? Return the exact label shown. Give the full label exactly as shown.
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 1 step before Iggy? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
+Answer format: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[382.802, 714.242, 504.802, 772.242]], "answer": "Gil"}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[382.802, 714.242, 504.802, 772.242]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[750.603, 691.254, 872.603, 749.254]], "answer": "Cida"}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[750.603, 691.254, 872.603, 749.254]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1047521225010981</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0010.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0010.json</t>
+      <c r="K17" t="n">
+        <v>6419815108582352</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0014.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0014.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="216.75" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="18" ht="216.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>before_k_steps</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps before Seed? Return the exact label shown. Return the exact visible label.
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Opal? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer format: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Opal? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[227.231, 614.0, 349.231, 672.0]], "answer": "Wyon"}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[227.231, 614.0, 349.231, 672.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6638190890293362</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0005.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="216.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps before Adna? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps before Adna? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[539.0, 739.0, 661.0, 797.0]], "answer": "Rhu"}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[539.0, 739.0, 661.0, 797.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6706193670556087</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0002.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="216.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 1 step before Mord? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 1 step before Mord? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[196.62, 411.746, 318.62, 469.746]], "answer": "Bala"}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[196.62, 411.746, 318.62, 469.746]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6968469141796444</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0007.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="216.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 3 steps before Fonz? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 3 steps before Fonz? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[820.459, 333.128, 942.459, 391.128]], "answer": "Roos"}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[820.459, 333.128, 942.459, 391.128]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7164956593535667</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0013.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="216.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps before Burd? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps before Burd? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[881.38, 411.746, 1003.38, 469.746]], "answer": "Mame"}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[881.38, 411.746, 1003.38, 469.746]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>7209459018694620</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0023.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="216.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps before Wang? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
+Answer: set "answer" to the exact visible stage label.
+Example JSON:
+{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps before Wang? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible stage label.
+Example JSON:
+{"answer":"Davi"}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[327.397, 691.254, 449.397, 749.254]], "answer": "Jago"}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[327.397, 691.254, 449.397, 749.254]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>7534642154558093</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0016.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="216.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_cycle_offset_stage_label</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>before_k_steps</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 5 steps before Lati? Return the exact label shown. Give the full label exactly as shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer rule: set "answer" to the exact visible stage label.
@@ -5054,63 +6142,63 @@
 {"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps before Seed? Return the exact label shown. Return the exact visible label.
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 5 steps before Lati? Return the exact label shown. Give the full label exactly as shown.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
+Answer format: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Etan"}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[539.0, 739.0, 661.0, 797.0]], "answer": "Eb"}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[539.0, 739.0, 661.0, 797.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1311641219581785</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0006.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0006.json</t>
+      <c r="K24" t="n">
+        <v>7784211536834367</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0011.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0011.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="216.75" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="25" ht="216.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>before_k_steps</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step before Doak? Return the exact label shown. Give the full label exactly as shown.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps before Akel? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer format: set "answer" to the exact visible stage label.
@@ -5118,63 +6206,63 @@
 {"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 1 step before Doak? Return the exact label shown. Give the full label exactly as shown.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps before Akel? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible stage label.
+Answer rule: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[257.541, 333.128, 379.541, 391.128]], "answer": "Blim"}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[257.541, 333.128, 379.541, 391.128]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[184.469, 445.588, 306.469, 503.588]], "answer": "Ewer"}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[184.469, 445.588, 306.469, 503.588]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1633263946054824</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0007.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0007.json</t>
+      <c r="K25" t="n">
+        <v>8091756162287753</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0001.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0001.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="216.75" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="26" ht="216.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_cycle_offset_stage_label</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>before_k_steps</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps before Issi? Return the exact label shown. Answer using the exact visible label.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 6 steps before Tham? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
 Answer: set "answer" to the exact visible stage label.
@@ -5182,1125 +6270,37 @@
 {"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps before Issi? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[850.769, 614.0, 972.769, 672.0]], "answer": "Sher"}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[850.769, 614.0, 972.769, 672.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2045654938436338</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0009.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="216.75" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps before Keen? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps before Keen? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[284.442, 312.223, 406.442, 370.223]], "answer": "Kado"}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[284.442, 312.223, 406.442, 370.223]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2989931902683007</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0003.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="216.75" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Roe? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Roe? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[850.769, 614.0, 972.769, 672.0]], "answer": "Lux"}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[850.769, 614.0, 972.769, 672.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3127034425673441</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0016.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="216.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 2 steps before God? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 2 steps before God? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 739.0, 661.0, 797.0]], "answer": "Ryle"}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 739.0, 661.0, 797.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3600691304852887</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0019.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="216.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps before Adon? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled clockwise cycle: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps before Adon? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Dumm"}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3895679011451700</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0004.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="216.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 6 steps before Jeaz? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Moving clockwise around the cycle, what stage is 6 steps before Jeaz? Return the exact label shown. Return the exact visible label.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 6 steps before Tham? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the exact visible stage label.
 Example JSON:
 {"answer":"Davi"}</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[257.541, 333.128, 379.541, 391.128]], "answer": "Im"}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[257.541, 333.128, 379.541, 391.128]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[307.596, 297.489, 429.596, 355.489]], "answer": "Max"}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[307.596, 297.489, 429.596, 355.489]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>3988457119670738</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0011.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="216.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps before Pyle? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 2 steps before Pyle? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Kyl"}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4234454412836436</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0005.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="216.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps before Eran? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 2 steps before Eran? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Darb"}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4903265744910559</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0001.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="216.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 5 steps before Wash? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 5 steps before Wash? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[889.974, 544.63, 1011.974, 602.63]], "answer": "Tedd"}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[889.974, 544.63, 1011.974, 602.63]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>5346591211111627</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0000.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="216.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps before Call? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer rule: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 4 steps before Call? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[793.558, 665.777, 915.558, 723.777]], "answer": "Nath"}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[793.558, 665.777, 915.558, 723.777]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>5642619739692902</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0015.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="216.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps before Kilk? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps before Kilk? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[793.558, 312.223, 915.558, 370.223]], "answer": "Roz"}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[793.558, 312.223, 915.558, 370.223]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>5859675207023172</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0020.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="216.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Ilse? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 3 steps before Ilse? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[539.0, 239.0, 661.0, 297.0]], "answer": "Eula"}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[539.0, 239.0, 661.0, 297.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>5981145901177103</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0002.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="216.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps before Arte? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 3 steps before Arte? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[227.231, 614.0, 349.231, 672.0]], "answer": "Kala"}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[227.231, 614.0, 349.231, 672.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>8036839965726897</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0008.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="216.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps before Con? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 4 steps before Con? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[850.769, 614.0, 972.769, 672.0]], "answer": "Nela"}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[850.769, 614.0, 972.769, 672.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>8178829660322333</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0021.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="216.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps before Ynes? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Follow the cycle order and answer: Moving clockwise around the cycle, what stage is 3 steps before Ynes? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[284.442, 665.777, 406.442, 723.777]], "answer": "Gant"}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[284.442, 665.777, 406.442, 723.777]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8514430820354414</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0012.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="216.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 7 steps before Moya? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the directed cycle diagram in the image: a clockwise cycle diagram with labeled stages connected by arrows. Use the cycle to answer: Moving clockwise around the cycle, what stage is 7 steps before Moya? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[850.769, 614.0, 972.769, 672.0]], "answer": "Gui"}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[850.769, 614.0, 972.769, 672.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8525038448447762</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0014.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="216.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps before Tima? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer requirement: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Read the directed cycle diagram and answer: Moving clockwise around the cycle, what stage is 4 steps before Tima? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[750.603, 691.254, 872.603, 749.254]], "answer": "Adda"}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[750.603, 691.254, 872.603, 749.254]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8853572978888852</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/images/before_k_steps/0024.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_cycle_offset_stage_label/data/before_k_steps/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="216.75" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_cycle_offset_stage_label</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>before_k_steps</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 7 steps before Kono? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct stage box.
-Answer field: set "answer" to the exact visible stage label.
-Example JSON:
-{"evidence":[[329,641,451,699]],"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>You are given a clockwise cycle diagram with labeled stages connected by arrows. Determine the requested stage from the cycle: Moving clockwise around the cycle, what stage is 7 steps before Kono? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible stage label.
-Example JSON:
-{"answer":"Davi"}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[327.397, 286.746, 449.397, 344.746]], "answer": "Ori"}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[327.397, 286.746, 449.397, 344.746]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8974942451533599</v>
+        <v>8465710675746272</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
